--- a/paper/supplementary/Supplementary_Data_1.xlsx
+++ b/paper/supplementary/Supplementary_Data_1.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,9 +68,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,57 +437,140 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Supplementary Data 1</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Source data for Supplementary Figures and reviewer-relevant benchmark tables in the DELT-Hit Nature Protocols supplementary notes.</t>
+          <t>Source data for the Supplementary Figures and supplementary comparison and benchmark tables.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Generated by</t>
+          <t>Supporting-material repository</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>paper/supplementary/build_submission_assets.py</t>
+          <t>https://doi.org/10.6084/m9.figshare.31198468</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NF2 rank source</t>
+          <t>DELT-Hit Zenodo archive</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>/home/leandro/projects/overleaf-delt-hit-review/supporting_material/experiments/favalli/benchmark_nf2/strict14_method_ranks.csv</t>
+          <t>https://doi.org/10.5281/zenodo.20447074</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Demultiplex source</t>
+          <t>example-single-stranded: Figshare article API</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>/home/leandro/projects/overleaf-delt-hit-review/benchmarks/demultiplex/tools</t>
+          <t>https://api.figshare.com/v2/articles/31198468</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>example-single-stranded: campaign.fastq.gz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://figshare.com/ndownloader/files/61487743</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>favalli: lane-1 FASTA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/9xZkcW5jWtLHiFo/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>favalli: published evaluation table</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/cgxBWkHnpkT6rBi/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pure-del: lane-1 FASTQ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/H8YB6wdxpwWgzLB/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pure-del: lane-2 FASTQ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/wK6t8qjDTay8rAg/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pure-del: published selection tables ZIP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://zenodo.org/records/11122901/files/Keller_Petrov_etal_Supplementary_Material2_Sequencing_Data.zip?download=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Generated by</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>manual README refresh; full workbook generator currently references removed NF2 assets</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6196,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6117,7 +6208,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6130,7 +6220,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6138,7 +6227,6 @@
           <t>Single-compound structure lookup</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -6156,7 +6244,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/paper/supplementary/Supplementary_Data_1.xlsx
+++ b/paper/supplementary/Supplementary_Data_1.xlsx
@@ -11,14 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppFig1_runtime_cycles" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppFig2_runtime_bbpc" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppFig3_peak_memory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppFig4_NF2_recall" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable1_Favalli" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable2_PureDEL" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable3_Workflow" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable4_NF2_truth" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable5_NF2_summary" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strict14_method_ranks" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zscore_benchmark" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable1_Favalli" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable2_PureDEL" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable3_Workflow" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable6_ReactionTemplates" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,14 +34,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -68,10 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,2079 +424,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Supplementary Data 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Source data for the Supplementary Figures and supplementary comparison and benchmark tables.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Supporting-material repository</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.6084/m9.figshare.31198468</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DELT-Hit Zenodo archive</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5281/zenodo.20447074</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>example-single-stranded: Figshare article API</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://api.figshare.com/v2/articles/31198468</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>example-single-stranded: campaign.fastq.gz</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://figshare.com/ndownloader/files/61487743</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>favalli: lane-1 FASTA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://polybox.ethz.ch/index.php/s/9xZkcW5jWtLHiFo/download</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>favalli: published evaluation table</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://polybox.ethz.ch/index.php/s/cgxBWkHnpkT6rBi/download</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>pure-del: lane-1 FASTQ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://polybox.ethz.ch/index.php/s/H8YB6wdxpwWgzLB/download</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>pure-del: lane-2 FASTQ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://polybox.ethz.ch/index.php/s/wK6t8qjDTay8rAg/download</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>pure-del: published selection tables ZIP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://zenodo.org/records/11122901/files/Keller_Petrov_etal_Supplementary_Material2_Sequencing_Data.zip?download=1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Generated by</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>manual README refresh; full workbook generator currently references removed NF2 assets</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>median_rank</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>worst_rank</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>recall_at_10</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>recall_at_50</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>recall_at_100</t>
-        </is>
-      </c>
+          <t>Supplementary Data 1</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DELT-Hit counts</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>31730</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9285714285714286</v>
+          <t>Source data for the Supplementary Figures, supplementary comparison and benchmark tables, and additional reaction templates.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DELT-Hit z-score</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>14</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>674</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9285714285714286</v>
+          <t>Supporting-material repository</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.6084/m9.figshare.31198468</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DELi NSC</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>14</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>425</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9285714285714286</v>
+          <t>Example single-stranded direct download</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://figshare.com/ndownloader/files/61487743</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DELi MLE</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>161254</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.5714285714285714</v>
+          <t>Download links used by supporting_material/experiments/*/download.sh</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DELT-Hit edgeR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>46</v>
-      </c>
-      <c r="D6" t="n">
-        <v>136360</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.5714285714285714</v>
+          <t>example-single-stranded/download.sh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://api.figshare.com/v2/articles/31198468 ; https://figshare.com/ndownloader/files/61487743</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DELi norm-z</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" t="n">
-        <v>113009</v>
-      </c>
-      <c r="D7" t="n">
-        <v>164061</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>paper_target</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>strand</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>paper_ab</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>delt_hit_counts_rank</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>delt_hit_zscore_rank</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>delt_hit_edger_rank</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>deli_nsc_rank</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>deli_mle_rank</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>deli_normz_rank</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>has_deli</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ss_caix</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>A160/B475</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>compound 8/10, Kd 7.2-8.8 nM</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>71210</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>276037</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ds_caix</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>A160/B475</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>compound 8/10, Kd 7.2-8.8 nM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>295122</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ss_caix</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>A69/B475</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>compound 12, Kd 68 nM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>71211</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>276037</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ds_caix</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>A69/B475</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>compound 12, Kd 68 nM</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>115270</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>295122</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ss_crebbp</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>A130/B99</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>compound 13, Kd 0.92 uM in main text</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>103315</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>291133</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ds_crebbp</t>
+          <t>favalli/download.sh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>A130/B99</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>compound 13, Kd 0.92 uM in main text</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>120867</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>297924</t>
+          <t>https://polybox.ethz.ch/index.php/s/9xZkcW5jWtLHiFo/download ; https://polybox.ethz.ch/index.php/s/cgxBWkHnpkT6rBi/download</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ss_crebbp</t>
+          <t>pure-del/download.sh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>A130/B128</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>compound 14, Kd 6.0 uM</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>291133</t>
+          <t>https://polybox.ethz.ch/index.php/s/H8YB6wdxpwWgzLB/download ; https://polybox.ethz.ch/index.php/s/wK6t8qjDTay8rAg/download ; https://zenodo.org/records/11122901/files/Keller_Petrov_etal_Supplementary_Material2_Sequencing_Data.zip?download=1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ds_crebbp</t>
+          <t>Generated by</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>A130/B128</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>compound 14, Kd 6.0 uM</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>120870</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>297924</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ss_wt_pik3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>wt-PI3K</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>A110/B489</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>compounds 16/17, Kd 306/126 nM</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8620</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>9794</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>113835</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>296385</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ds_wt_pik3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wt-PI3K</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>A110/B489</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>compounds 16/17, Kd 306/126 nM</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20564</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>23974</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>114261</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>294594</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ss_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>A110/B319</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>compounds 22/23, ELISA 0.19/0.37 uM</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10333</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>7225</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>111592</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>295033</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ds_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>A110/B319</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>compounds 22/23, ELISA 0.19/0.37 uM</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>84035</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>94491</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>123779</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>298497</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ss_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>ss</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>A110/B157</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>compounds 20/21, ELISA 3.6/3.0 uM</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>64188</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>33075</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>112183</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>295033</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ds_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ds</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>A110/B157</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>compounds 20/21, ELISA 3.6/3.0 uM</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>31730</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>136360</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>161254</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>164061</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>298497</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>experiment</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>paper_target</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>paper_ab</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>label</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>code_0</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>code_1</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>zscore_rank</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>zscore_value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ss_caix</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A160/B475</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4.036</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ds_caix</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A160/B475</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ss_caix</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A69/B475</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2.707</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ds_caix</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A69/B475</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>474</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2.648</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ss_crebbp</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A130/B99</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.239</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ds_crebbp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>A130/B99</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.169</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ss_crebbp</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A130/B128</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.121</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ds_crebbp</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>A130/B128</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.108</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ss_wt_pik3</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>wt-PI3K</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>A110/B489</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.104</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ds_wt_pik3</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>wt-PI3K</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>A110/B489</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ss_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>A110/B319</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.108</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ds_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>A110/B319</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.019</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ss_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>A110/B157</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.092</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ds_h1047r_pik3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>A110/B157</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>strict_affinity</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.008</t>
+          <t>paper/supplementary/build_submission_assets.py</t>
         </is>
       </c>
     </row>
@@ -5170,412 +3178,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>tool_family</t>
+          <t>code_0</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>method</t>
+          <t>code_1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>rank_cutoff</t>
+          <t>legacy</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>delt</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>identical</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DELT-Hit counts</t>
-        </is>
+      <c r="A2" t="n">
+        <v>268</v>
+      </c>
+      <c r="B2" t="n">
+        <v>278</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E2" t="n">
-        <v>14</v>
+        <v>62</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DELT-Hit counts</t>
-        </is>
+      <c r="A3" t="n">
+        <v>67</v>
+      </c>
+      <c r="B3" t="n">
+        <v>278</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E3" t="n">
-        <v>14</v>
+        <v>59</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DELT-Hit counts</t>
-        </is>
+      <c r="A4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
       </c>
       <c r="C4" t="n">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E4" t="n">
-        <v>14</v>
+        <v>53</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DELT-Hit z-score</t>
-        </is>
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>278</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E5" t="n">
-        <v>14</v>
+        <v>51</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DELT-Hit z-score</t>
-        </is>
+      <c r="A6" t="n">
+        <v>268</v>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
       </c>
       <c r="C6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14</v>
+        <v>49</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DELT-Hit z-score</t>
-        </is>
+      <c r="A7" t="n">
+        <v>204</v>
+      </c>
+      <c r="B7" t="n">
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14</v>
+        <v>47</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DELi NSC</t>
-        </is>
+      <c r="A8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B8" t="n">
+        <v>304</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="E8" t="n">
-        <v>14</v>
+        <v>43</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DELi NSC</t>
-        </is>
+      <c r="A9" t="n">
+        <v>193</v>
+      </c>
+      <c r="B9" t="n">
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E9" t="n">
-        <v>14</v>
+        <v>42</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>DELi NSC</t>
-        </is>
+      <c r="A10" t="n">
+        <v>67</v>
+      </c>
+      <c r="B10" t="n">
+        <v>230</v>
       </c>
       <c r="C10" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="E10" t="n">
-        <v>14</v>
+        <v>42</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DELi MLE</t>
-        </is>
+      <c r="A11" t="n">
+        <v>268</v>
+      </c>
+      <c r="B11" t="n">
+        <v>230</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="E11" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>DELi MLE</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>50</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E12" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>DELi MLE</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>100</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DELT-Hit edgeR</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="E14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>DELT-Hit edgeR</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DELT-Hit</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DELT-Hit edgeR</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>100</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="E16" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DELi norm-z</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E17" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>DELi norm-z</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>50</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E18" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DELi</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DELi norm-z</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>100</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14</v>
+        <v>39</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5589,7 +3389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5605,15 +3405,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>code_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>legacy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delt</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>identical</t>
         </is>
@@ -5621,171 +3426,201 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
-      </c>
-      <c r="E2" t="b">
+        <v>82237</v>
+      </c>
+      <c r="E2" t="n">
+        <v>82237</v>
+      </c>
+      <c r="F2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>278</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
-      </c>
-      <c r="E3" t="b">
+        <v>75428</v>
+      </c>
+      <c r="E3" t="n">
+        <v>75428</v>
+      </c>
+      <c r="F3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
-      </c>
-      <c r="E4" t="b">
+        <v>69178</v>
+      </c>
+      <c r="E4" t="n">
+        <v>69178</v>
+      </c>
+      <c r="F4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>278</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
-      </c>
-      <c r="E5" t="b">
+        <v>66951</v>
+      </c>
+      <c r="E5" t="n">
+        <v>66951</v>
+      </c>
+      <c r="F5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>268</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>49</v>
-      </c>
-      <c r="E6" t="b">
+        <v>63161</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63161</v>
+      </c>
+      <c r="F6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>204</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
-      </c>
-      <c r="E7" t="b">
+        <v>63147</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63147</v>
+      </c>
+      <c r="F7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
-      </c>
-      <c r="E8" t="b">
+        <v>58942</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58942</v>
+      </c>
+      <c r="F8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>193</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
-      </c>
-      <c r="E9" t="b">
+        <v>55386</v>
+      </c>
+      <c r="E9" t="n">
+        <v>55386</v>
+      </c>
+      <c r="F9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>230</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
-      </c>
-      <c r="E10" t="b">
+        <v>53387</v>
+      </c>
+      <c r="E10" t="n">
+        <v>53387</v>
+      </c>
+      <c r="F10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>268</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>39</v>
-      </c>
-      <c r="E11" t="b">
+        <v>49307</v>
+      </c>
+      <c r="E11" t="n">
+        <v>49307</v>
+      </c>
+      <c r="F11" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5800,240 +3635,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>code_0</t>
+          <t>feature</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>code_1</t>
+          <t>delt_hit</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>code_2</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>legacy</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>delt</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>identical</t>
+          <t>deli</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>82237</v>
-      </c>
-      <c r="E2" t="n">
-        <v>82237</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Input files</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Excel workbook compiled to config.yaml</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Library JSON, building-block CSV files, and decode-settings YAML</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" t="n">
-        <v>11</v>
-      </c>
-      <c r="D3" t="n">
-        <v>75428</v>
-      </c>
-      <c r="E3" t="n">
-        <v>75428</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>User-friendliness</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Single workbook keeps library design, barcode definitions, and analyses in one file</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>More modular and explicit, but usually requires editing several structured input files</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" t="n">
-        <v>69178</v>
-      </c>
-      <c r="E4" t="n">
-        <v>69178</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Raw read decoding</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="n">
-        <v>66951</v>
-      </c>
-      <c r="E5" t="n">
-        <v>66951</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Error-tolerant barcode matching</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" t="n">
-        <v>11</v>
-      </c>
-      <c r="D6" t="n">
-        <v>63161</v>
-      </c>
-      <c r="E6" t="n">
-        <v>63161</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Library enumeration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" t="n">
-        <v>11</v>
-      </c>
-      <c r="D7" t="n">
-        <v>63147</v>
-      </c>
-      <c r="E7" t="n">
-        <v>63147</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Enrichment / analysis methods</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Counts-based enrichment, normalized z-score, and edgeR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MLE, NSC/SD_min, normalized z-score, log-space z-score, PolyO, overlap analyses</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>9</v>
-      </c>
-      <c r="B8" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" t="n">
-        <v>11</v>
-      </c>
-      <c r="D8" t="n">
-        <v>58942</v>
-      </c>
-      <c r="E8" t="n">
-        <v>58942</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Analysis reports</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Organized analysis folders and static outputs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Automated HTML report with figures and CSV exports</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11</v>
-      </c>
-      <c r="D9" t="n">
-        <v>55386</v>
-      </c>
-      <c r="E9" t="n">
-        <v>55386</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Dual-Display</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7</v>
-      </c>
-      <c r="C10" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" t="n">
-        <v>53387</v>
-      </c>
-      <c r="E10" t="n">
-        <v>53387</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Counts-driven filtered enumeration</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" t="n">
-        <v>49307</v>
-      </c>
-      <c r="E11" t="n">
-        <v>49307</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Interactive count-table dashboard</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Single-compound structure lookup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Molecular property and representation generation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6046,419 +3850,187 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>delt_hit</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>deli</t>
+          <t>smirks</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Input files</t>
+          <t>MTT deprotection</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Excel workbook compiled to config.yaml</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Library JSON, building-block CSV files, and decode-settings YAML</t>
+          <t>[N:1]C(c1ccccc1)(c2ccccc2)c3ccc(C)cc3&gt;&gt;[N:1]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>User-friendliness</t>
+          <t>Nvoc deprotection</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Single workbook keeps library design, barcode definitions, and analyses in one file</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>More modular and explicit, but usually requires editing several structured input files</t>
+          <t>[N:1]C(OCc1cc(OC)c(OC)cc1[N+]([O-])=O)=O&gt;&gt;[N:1]</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Raw read decoding</t>
+          <t>Fmoc deprotection</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>[N:1]C(OCC1c2c(c3c1cccc3)cccc2)=O&gt;&gt;[N:1]</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Error-tolerant barcode matching</t>
+          <t>Staudinger reduction</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>[#6:1][$([NX2-][NX2+]#[NX1]),$([NX2]=[NX2+]=[NX1-])]&gt;&gt;[#6:1][N;H2]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Library enumeration</t>
+          <t>Azido transfer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>[#6:1][N;H2:2]&gt;&gt;[#6:1][N:2]=[N+]=[N-]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enrichment / analysis methods</t>
+          <t>Nitro reduction</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Counts-based enrichment, normalized z-score, and edgeR</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MLE, NSC/SD_min, normalized z-score, log-space z-score, PolyO, overlap analyses</t>
+          <t>[#6:1][N+]([O-])=O&gt;&gt;[#6:1][N;H2]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analysis reports</t>
+          <t>Ester cleavage</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Organized analysis folders and static outputs</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Automated HTML report with figures and CSV exports</t>
+          <t>[CX3:1](=[O:2])[OX2;H0][$([C;H3]),$([C;H2][C;H3]),$([C;H0]([C;H3])([C;H3])[C;H3])]&gt;&gt;[CX3:1](=[O:2])[OX2;H1]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dual-Display</t>
+          <t>Reductive amination</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>[C$(C(=O)([CX4,c])([CX4,c])),C$([CH](=O)([CX4,c])):1](=[O]).[N:2]&gt;&gt;[C:1][N:2]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Counts-driven filtered enumeration</t>
+          <t>Heck</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>[cX3:1][Br,I].[CX3:2]=[CX3;H2:3]&gt;&gt;[cX3:1]-[CX3:3]=[CX3:2]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Interactive count-table dashboard</t>
+          <t>Thioether formation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>[#6:1][S;H1:2].[C:3][Cl,Br,I]&gt;&gt;[#6:1][S:2][C:3]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Single-compound structure lookup</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>Amide bond formation</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>[CX3:1](=[O:2])[OX2;H1].[N;$([N;H1,H2]),$([N;H3]):4]&gt;&gt;[CX3:1](=[O:2])[N:4]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Molecular property and representation generation</t>
+          <t>Sonogashira</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>target</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ab_pair</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>evidence</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>conditions</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>instances</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A160/B475</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>compound 8/10, Kd 7.2-8.8 nM</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CAIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A69/B475</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>compound 12, Kd 68 nM</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A130/B99</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>compound 13, Kd 0.92 uM in main text</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CREBBP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A130/B128</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>compound 14, Kd 6.0 uM</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>wt-PI3K</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>A110/B489</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>compounds 16/17, Kd 306/126 nM</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>A110/B319</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>compounds 22/23, ELISA 0.19/0.37 uM</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>H1047R-PI3K</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A110/B157</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>compounds 20/21, ELISA 3.6/3.0 uM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ss, ds</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
+          <t>[cX3:1][Br,I].[CX2:2]#[CX2;H1:3]&gt;&gt;[cX3:1]-[CX2:3]#[CX2:2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Suzuki</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>[cX3:1][Br,I].[#6:2][BX3]&gt;&gt;[cX3:1][#6:2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C-N coupling reactions</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>[cX3:1][Cl,Br,I].[N;H1,H2;!$(NC=O);!$(NS=O):2]&gt;&gt;[cX3:1][N:2]</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/paper/supplementary/Supplementary_Data_1.xlsx
+++ b/paper/supplementary/Supplementary_Data_1.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,77 +445,101 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Supporting-material repository</t>
+          <t>Workflow data archive (Zenodo)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://doi.org/10.6084/m9.figshare.31198468</t>
+          <t>https://doi.org/10.5281/zenodo.20447074</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Example single-stranded direct download</t>
+          <t>Code release archive (Zenodo)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://figshare.com/ndownloader/files/61487743</t>
+          <t>https://doi.org/10.5281/zenodo.20497548</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Download links used by supporting_material/experiments/*/download.sh</t>
+          <t>Supporting-material repository</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.6084/m9.figshare.31198468</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>example-single-stranded/download.sh</t>
+          <t>Example single-stranded direct download</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://api.figshare.com/v2/articles/31198468 ; https://figshare.com/ndownloader/files/61487743</t>
+          <t>https://ndownloader.figshare.com/files/61487743</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>favalli/download.sh</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://polybox.ethz.ch/index.php/s/9xZkcW5jWtLHiFo/download ; https://polybox.ethz.ch/index.php/s/cgxBWkHnpkT6rBi/download</t>
+          <t>Download links used by supporting_material/experiments/*/download.sh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>pure-del/download.sh</t>
+          <t>example-single-stranded/download.sh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://polybox.ethz.ch/index.php/s/H8YB6wdxpwWgzLB/download ; https://polybox.ethz.ch/index.php/s/wK6t8qjDTay8rAg/download ; https://zenodo.org/records/11122901/files/Keller_Petrov_etal_Supplementary_Material2_Sequencing_Data.zip?download=1</t>
+          <t>https://api.figshare.com/v2/articles/31198468 ; https://ndownloader.figshare.com/files/61487743</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>favalli/download.sh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/9xZkcW5jWtLHiFo/download ; https://polybox.ethz.ch/index.php/s/cgxBWkHnpkT6rBi/download</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>pure-del/download.sh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://polybox.ethz.ch/index.php/s/H8YB6wdxpwWgzLB/download ; https://polybox.ethz.ch/index.php/s/wK6t8qjDTay8rAg/download ; https://zenodo.org/records/11122901/files/Keller_Petrov_etal_Supplementary_Material2_Sequencing_Data.zip?download=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Generated by</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>paper/supplementary/build_submission_assets.py</t>
         </is>

--- a/paper/supplementary/Supplementary_Data_1.xlsx
+++ b/paper/supplementary/Supplementary_Data_1.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SuppTable6_ReactionTemplates" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -33,7 +32,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -425,7 +427,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="100.83203125" bestFit="1" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -500,7 +505,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>example-single-stranded/download.sh</t>
+          <t>example-single-display/download.sh</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -557,7 +562,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1393,7 +1398,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -2229,7 +2234,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3203,7 +3208,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3414,7 +3419,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3660,7 +3665,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3809,7 +3814,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3822,7 +3826,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3835,7 +3838,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3843,7 +3845,6 @@
           <t>Single-compound structure lookup</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>yes</t>
@@ -3861,7 +3862,6 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3875,7 +3875,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
